--- a/unterlagen/Energie/Energie_calc.xlsx
+++ b/unterlagen/Energie/Energie_calc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\appel\Documents\GitHub\Moin-MINT\unterlagen\Energie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11D9A71E-DDF2-49E0-856D-9488E23ECA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACABC41-2417-403B-A416-5FE9A50763DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1485" yWindow="4935" windowWidth="21840" windowHeight="15345" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29055" yWindow="150" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flächenbedarf" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="38">
   <si>
     <t>Bundesbürger</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Anteil %</t>
   </si>
   <si>
-    <t>ersparte Wärmeentergie</t>
-  </si>
-  <si>
     <t>Gesamtwärmeenergie pro BB und Tag</t>
   </si>
   <si>
@@ -148,6 +145,12 @@
   </si>
   <si>
     <t>Statista Mrd. €</t>
+  </si>
+  <si>
+    <t>Wärmeenergie</t>
+  </si>
+  <si>
+    <t>ersparte Energie</t>
   </si>
 </sst>
 </file>
@@ -219,14 +222,14 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Komma" xfId="1" builtinId="3"/>
@@ -549,11 +552,11 @@
       <c r="B5">
         <v>16</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
@@ -664,11 +667,11 @@
       <c r="B17">
         <v>8</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
@@ -779,11 +782,11 @@
       <c r="B29">
         <v>150</v>
       </c>
-      <c r="C29" s="9" t="s">
+      <c r="C29" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C30" t="s">
@@ -903,19 +906,19 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
@@ -925,7 +928,10 @@
         <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -936,67 +942,88 @@
         <f>$A$3*B4/100</f>
         <v>0.85</v>
       </c>
-      <c r="D4" s="1"/>
+      <c r="D4" s="4">
+        <f t="shared" ref="D4:D9" si="0">C4/3*2</f>
+        <v>0.56666666666666665</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>10</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" ref="C5:C10" si="0">$A$3*B5/100</f>
+        <f t="shared" ref="C5:C10" si="1">$A$3*B5/100</f>
         <v>1.7</v>
       </c>
-      <c r="D5" s="1"/>
+      <c r="D5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1333333333333333</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>20</v>
       </c>
       <c r="C6" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.4</v>
       </c>
-      <c r="D6" s="1"/>
+      <c r="D6" s="4">
+        <f t="shared" si="0"/>
+        <v>2.2666666666666666</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>30</v>
       </c>
       <c r="C7" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.0999999999999996</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="4">
+        <f t="shared" si="0"/>
+        <v>3.4</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>50</v>
       </c>
       <c r="C8" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8.5</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="4">
+        <f t="shared" si="0"/>
+        <v>5.666666666666667</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>80</v>
       </c>
       <c r="C9" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>13.6</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="4">
+        <f t="shared" si="0"/>
+        <v>9.0666666666666664</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>100</v>
       </c>
       <c r="C10" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="4">
+        <f>C10/3*2</f>
+        <v>11.333333333333334</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1018,7 +1045,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1">
         <v>24</v>
@@ -1031,15 +1058,15 @@
       <c r="B2">
         <v>84669000</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
+      <c r="C2" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5">
         <v>1000000000</v>
@@ -1050,7 +1077,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="6">
         <f>B3*B1/B2/1000</f>
@@ -1060,10 +1087,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1183,76 +1210,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="D1" s="11">
+      <c r="D1" s="9">
         <f>D2*0.04/10^9</f>
         <v>79.48888888888888</v>
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="5">
         <f>SUM(D4:D7)</f>
         <v>1987222222222.2222</v>
       </c>
       <c r="K2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L2" s="5">
         <f>SUM(L4:L7)</f>
         <v>86533592397.861404</v>
       </c>
-      <c r="M2" s="11">
+      <c r="M2" s="9">
         <f>SUM(M4:M7)</f>
         <v>86.533592397861412</v>
       </c>
-      <c r="N2" s="11">
+      <c r="N2" s="9">
         <f>SUM(N4:N7)</f>
         <v>75.213189012188465</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
         <v>35</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4">
         <v>875</v>
@@ -1261,11 +1288,11 @@
         <f>C4/(3.6*10^6)*10^15</f>
         <v>243055555555.55554</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <f>D4/365/84669000</f>
         <v>7.8648103988361298</v>
       </c>
-      <c r="F4" s="12"/>
+      <c r="F4" s="10"/>
       <c r="H4">
         <v>236</v>
       </c>
@@ -1284,18 +1311,18 @@
         <f>K4*D4</f>
         <v>7513189012.1884661</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="9">
         <f>L4/10^9</f>
         <v>7.5131890121884659</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="9">
         <f>M4</f>
         <v>7.5131890121884659</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>-21</v>
@@ -1304,17 +1331,17 @@
         <f t="shared" ref="D5:D7" si="0">C5/(3.6*10^6)*10^15</f>
         <v>-5833333333.333333</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <f t="shared" ref="E5:E7" si="1">D5/365/84669000</f>
         <v>-0.18875544957206711</v>
       </c>
-      <c r="F5" s="12"/>
+      <c r="F5" s="10"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="11"/>
+      <c r="M5" s="9"/>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>3797</v>
@@ -1323,11 +1350,11 @@
         <f t="shared" si="0"/>
         <v>1054722222222.2223</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <f t="shared" si="1"/>
         <v>34.128782953578046</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>80</v>
       </c>
       <c r="G6">
@@ -1339,11 +1366,11 @@
         <v>4.7233987934796565E-2</v>
       </c>
       <c r="L6" s="5">
-        <f t="shared" ref="L5:L7" si="2">K6*D6</f>
+        <f t="shared" ref="L6:L7" si="2">K6*D6</f>
         <v>49818736719.006271</v>
       </c>
-      <c r="M6" s="11">
-        <f t="shared" ref="M5:M7" si="3">L6/10^9</f>
+      <c r="M6" s="9">
+        <f t="shared" ref="M6:M7" si="3">L6/10^9</f>
         <v>49.818736719006274</v>
       </c>
       <c r="N6">
@@ -1352,7 +1379,7 @@
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>2503</v>
@@ -1361,11 +1388,11 @@
         <f t="shared" si="0"/>
         <v>695277777777.77771</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <f t="shared" si="1"/>
         <v>22.497851918042095</v>
       </c>
-      <c r="F7" s="12"/>
+      <c r="F7" s="10"/>
       <c r="K7">
         <v>4.2000000000000003E-2</v>
       </c>
@@ -1373,7 +1400,7 @@
         <f t="shared" si="2"/>
         <v>29201666666.666664</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="9">
         <f t="shared" si="3"/>
         <v>29.201666666666664</v>
       </c>
